--- a/outputs/Star_Fandom_FY2025-26_Tally_vs_Financials_vs_Winman.xlsx
+++ b/outputs/Star_Fandom_FY2025-26_Tally_vs_Financials_vs_Winman.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Tally TB as exported (TrialBal.xlsx)</t>
+          <t>Tally TB as exported (TrialBal.xlsx, latest)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -696,27 +696,27 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Unsecured loan from Samartha Raghava Nagabhushanam (long-term)</t>
+          <t>Provisions (Tally group) - Short-term provisions</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7">
         <f>B8+C8</f>
         <v/>
       </c>
       <c r="E8" s="6" t="n">
-        <v>250000</v>
+        <v>450000</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>250000</v>
+        <v>450000</v>
       </c>
       <c r="H8" s="7">
         <f>F8+G8</f>
@@ -980,27 +980,27 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Receivable from partners (capital) - opening 2,00,000 settled during the year</t>
+          <t>Receivable from partners (capital contribution)</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D17" s="7">
         <f>B17+C17</f>
         <v/>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="H17" s="7">
         <f>F17+G17</f>
@@ -1405,14 +1405,14 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Business promotion</t>
+          <t>Branding Expense (Winman: 'Business Expenses')</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>225000</v>
+        <v>0</v>
       </c>
       <c r="D30" s="7">
         <f>B30+C30</f>
@@ -1439,14 +1439,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Business expenses</t>
+          <t>Business Promotion</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>225000</v>
+        <v>0</v>
       </c>
       <c r="D31" s="7">
         <f>B31+C31</f>
@@ -1592,26 +1592,47 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Partners' contribution (capital): Winman has one 'Partners' capital' field: contribution 2,00,000 less current account 13,719 = 1,86,281</t>
+          <t>Partners' contribution (capital): Not in Tally (no opening balances); Rs 2,00,000 b/f from signed FY 2024-25 accounts. Winman has one 'Partners' capital' field: 2,00,000 less loss 13,719 = 1,86,281</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Sponsorship Amount - Sale of services: Winman: move 9,23,729 from 'Sale of products/goods' to 'Sale of services'</t>
+          <t>Provisions (Tally group) - Short-term provisions: Tally: credit side of Branding Expense and Business Promotion (2,25,000 each)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Mobile Expenses (Telephone): Financials: 3,918.50 less Tally round off 0.22 = 3,918.28, shown as 3,918</t>
+          <t>Receivable from partners (capital contribution): B/f from FY 2024-25; still receivable. Winman: enter under 'Other current assets'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Sponsorship Amount - Sale of services: Winman: move 9,23,729 from 'Sale of products/goods' to 'Sale of services'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Mobile Expenses (Telephone): Financials: 3,918.50 less Tally round off 0.22 = 3,918.28, shown as 3,918</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Column B (Tally as exported) shows a difference of (13,719.42) on the check row only because the loss still sits in Tally's P&amp;L; it moves to the partners' current accounts when entry 2 on sheet 2 is posted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Tally 'after entries' keeps paise; the financials and Winman are in whole rupees (nearest rupee). Winman as exported cut off the paise on Advances (.61) and Bank (.76) - that is the source of the earlier Rs 2 difference.</t>
         </is>
@@ -1641,7 +1662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1655,7 +1676,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>A. Entries to post in Tally (FY 2025-26) so the books agree with the financial statements</t>
+          <t>A. Entries still to post in Tally (FY 2025-26) - the Rs 4,50,000 expenses and provision are already in Tally</t>
         </is>
       </c>
     </row>
@@ -1735,21 +1756,21 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>During FY</t>
+          <t>31-03-2026</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Business promotion</t>
+          <t>Partners' Current Account - Pramod (20%)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>225000</v>
+        <v>2743.88</v>
       </c>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Business expenses paid by partners on behalf of the LLP</t>
+          <t>Loss for the year Rs 13,719.42 (books, with paise) shared 20:50:15:15</t>
         </is>
       </c>
     </row>
@@ -1758,11 +1779,11 @@
       <c r="B7" s="8" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Business expenses</t>
+          <t>Partners' Current Account - Samartha (50%)</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>225000</v>
+        <v>6859.71</v>
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1772,180 +1793,184 @@
       <c r="B8" s="8" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   To Receivable from Partners (capital contribution) - settled</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Capital contribution of Rs 2,00,000 treated as paid</t>
-        </is>
-      </c>
+          <t>Partners' Current Account - Nithin (15%)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2057.91</v>
+      </c>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="8" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   To Unsecured Loan - Samartha Raghava Nagabhushanam (new ledger, long-term, no interest)</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="6" t="n">
-        <v>250000</v>
-      </c>
+          <t>Partners' Current Account - Varun (15%)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2057.92</v>
+      </c>
+      <c r="E9" s="7" t="n"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Keep separate from the existing 'Loan From Samarha...' ledger, which stays at Dr 4,09,311.61</t>
+          <t>Rounding paise placed here so the total is exact</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Partners' Current Account - Pramod (20%)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>2743.88</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Loss for the year Rs 13,719.42 (books, with paise) shared 20:50:15:15</t>
-        </is>
-      </c>
+          <t xml:space="preserve">   To Profit &amp; Loss A/c</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="6" t="n">
+        <v>13719.42</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Partners' Current Account - Samartha (50%)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>6859.71</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="D11" s="19">
+        <f>SUM(D4:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>SUM(E4:E10)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>IF(ABS(D11-E11)&lt;0.005,"Debits = Credits","NOT BALANCED")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Partners' Current Account - Nithin (15%)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>2057.91</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Partners' Current Account - Varun (15%)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>2057.92</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Rounding paise placed here so the total is exact</t>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Note: the loss in the books is Rs 13,719.42; the financial statements show it rounded to Rs 13,719 (split 2,743.80 / 6,859.50 / 2,057.85 / 2,057.85).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   To Profit &amp; Loss A/c</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="n">
-        <v>13719.42</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>B. Corrections to make in Winman (ITR-5, A.Y. 2026-27)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Totals</t>
-        </is>
-      </c>
-      <c r="D15" s="19">
-        <f>SUM(D4:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="19">
-        <f>SUM(E4:E14)</f>
-        <v/>
-      </c>
-      <c r="F15">
-        <f>IF(ABS(D15-E15)&lt;0.005,"Debits = Credits","NOT BALANCED")</f>
-        <v/>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Winman sheet / field</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>As exported</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Change to</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Note: the loss in the books is Rs 13,719.42; the financial statements show it rounded to Rs 13,719 (split 2,743.80 / 6,859.50 / 2,057.85 / 2,057.85).</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Balance Sheet - Partners' / Members' capital</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>186281</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Contribution 2,00,000 less share of loss 13,719 (Notes 3A + 3B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Balance Sheet - Other Provisions - Others</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Provisions as per Tally (Note 7A)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>B. Corrections to make in Winman (ITR-5, A.Y. 2026-27)</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Balance Sheet - Other current assets (sub-table): Receivable from partners</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Capital contribution receivable (Note 10A)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Winman sheet / field</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>As exported</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>Change to</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Balance Sheet - Loans &amp; advances - Advances</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>409311</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>409312</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Tally 4,09,311.61 rounded to the nearest rupee</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Balance Sheet - Partners' / Members' capital</t>
+          <t>Balance Sheet - Loans &amp; advances - Balance with Revenue Authorities</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
@@ -1954,188 +1979,110 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>186281</v>
+        <v>18475</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Contribution 2,00,000 less share of loss 13,719 (Notes 3A + 3B)</t>
+          <t>TDS 2025-26 receivable (Tally)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Balance Sheet - Unsecured loans - Others</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
+          <t>Balance Sheet - Cash / cash equivalents - Balances with Banks</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>45672</v>
       </c>
       <c r="C21" s="21" t="n">
-        <v>250000</v>
+        <v>45673</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Long-term interest-free loan from Samartha (Note 5)</t>
+          <t>Tally 45,672.76 rounded to the nearest rupee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Balance Sheet - Additional data - Unsecured Rupee Loans from persons u/s 40A(2)(b)</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
+          <t>Balance Sheet - Cash / cash equivalents - Others</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>18475</v>
       </c>
       <c r="C22" s="21" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Samartha is a partner - a specified person u/s 40A(2)(b)</t>
+          <t>This is TDS receivable, not cash</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Balance Sheet - Loans &amp; advances - Advances</t>
+          <t>Balance Sheet - Profit and loss A/c (Dr)</t>
         </is>
       </c>
       <c r="B23" s="21" t="n">
-        <v>409311</v>
+        <v>13721</v>
       </c>
       <c r="C23" s="21" t="n">
-        <v>409312</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Tally 4,09,311.61 rounded to the nearest rupee</t>
+          <t>Loss transferred to partners' current accounts (included in capital above)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Balance Sheet - Loans &amp; advances - Balance with Revenue Authorities</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
+          <t>P&amp;L - Sale of products/goods</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="n">
+        <v>923729</v>
       </c>
       <c r="C24" s="21" t="n">
-        <v>18475</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TDS 2025-26 receivable (Tally)</t>
+          <t>Sponsorship income is a service</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Balance Sheet - Cash / cash equivalents - Balances with Banks</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="n">
-        <v>45672</v>
+          <t>P&amp;L - Sale of services (excluding Professional receipts)</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>45673</v>
+        <v>923729</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Tally 45,672.76 rounded to the nearest rupee</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Balance Sheet - Cash / cash equivalents - Others</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="n">
-        <v>18475</v>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>This is TDS receivable, not cash</t>
+          <t>Sponsorship Amount (Tally)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Balance Sheet - Profit and loss A/c (Dr)</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="n">
-        <v>13721</v>
-      </c>
-      <c r="C27" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Loss transferred to partners' current accounts (included in capital above)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>P&amp;L - Sale of products/goods</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="n">
-        <v>923729</v>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Sponsorship income is a service</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>P&amp;L - Sale of services (excluding Professional receipts)</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>923729</v>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Sponsorship Amount (Tally)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Everything else in Winman (expenses 9,37,448, trade creditors 28,229, other payables 8,950) already matches and needs no change. After these corrections Winman's Balance Sheet totals 4,73,460 on both sides.</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Everything else in Winman (expenses 9,37,448, trade creditors 28,229, other payables 8,950) already matches and needs no change. After these corrections Winman's Balance Sheet totals 6,73,460 on both sides.</t>
         </is>
       </c>
     </row>

--- a/outputs/Star_Fandom_FY2025-26_Tally_vs_Financials_vs_Winman.xlsx
+++ b/outputs/Star_Fandom_FY2025-26_Tally_vs_Financials_vs_Winman.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Tally TB as exported (TrialBal.xlsx, latest)</t>
+          <t>Tally TB as exported (Trial_balance_as_per_their_tally.xlsx)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Provisions (Tally group) - Short-term provisions</t>
+          <t>Provisions (Tally group): Branding Charges Payable 2,25,000 + Business Promotion Payable 2,25,000</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -730,7 +730,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Sundry creditors / Trade payables</t>
+          <t>Sundry creditors / Trade payables: Bharathi Air Tel 4,623.82 + Cashfree Payments India Pvt Ltd 23,605.51</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -1599,40 +1599,33 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Provisions (Tally group) - Short-term provisions: Tally: credit side of Branding Expense and Business Promotion (2,25,000 each)</t>
+          <t>Receivable from partners (capital contribution): B/f from FY 2024-25; still receivable. Winman: enter under 'Other current assets'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Receivable from partners (capital contribution): B/f from FY 2024-25; still receivable. Winman: enter under 'Other current assets'</t>
+          <t>Sponsorship Amount - Sale of services: Winman: move 9,23,729 from 'Sale of products/goods' to 'Sale of services'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Sponsorship Amount - Sale of services: Winman: move 9,23,729 from 'Sale of products/goods' to 'Sale of services'</t>
+          <t>Mobile Expenses (Telephone): Financials: 3,918.50 less Tally round off 0.22 = 3,918.28, shown as 3,918</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Mobile Expenses (Telephone): Financials: 3,918.50 less Tally round off 0.22 = 3,918.28, shown as 3,918</t>
+          <t>Column B (Tally as exported) shows a difference of (13,719.42) on the check row only because the loss still sits in Tally's P&amp;L; it moves to the partners' current accounts when entry 2 on sheet 2 is posted.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Column B (Tally as exported) shows a difference of (13,719.42) on the check row only because the loss still sits in Tally's P&amp;L; it moves to the partners' current accounts when entry 2 on sheet 2 is posted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Tally 'after entries' keeps paise; the financials and Winman are in whole rupees (nearest rupee). Winman as exported cut off the paise on Advances (.61) and Bank (.76) - that is the source of the earlier Rs 2 difference.</t>
         </is>
